--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_45_R5.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_45_R5.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2755</v>
+        <v>3.1211</v>
       </c>
       <c r="E2" t="n">
-        <v>3.8033</v>
+        <v>3.4808</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5278</v>
+        <v>-0.3597</v>
       </c>
       <c r="G2" t="n">
         <v>3.3045</v>
@@ -610,13 +610,13 @@
         <v>1.8556</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0136</v>
+        <v>-0.168</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2284</v>
+        <v>-0.094</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.242</v>
+        <v>-0.074</v>
       </c>
       <c r="V2" t="n">
         <v>1.6083</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>K. JONES</t>
+          <t>J. LOYD</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9068</v>
+        <v>2.1851</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0475</v>
+        <v>3.1879</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1407</v>
+        <v>-1.0028</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1881</v>
+        <v>-1.1088</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1814</v>
+        <v>-1.1824</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0068</v>
+        <v>0.0736</v>
       </c>
       <c r="J3" t="n">
-        <v>1.2963</v>
+        <v>0.4322</v>
       </c>
       <c r="K3" t="n">
-        <v>1.0755</v>
+        <v>0.091</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2208</v>
+        <v>0.3412</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.1082</v>
+        <v>-1.5409</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8942</v>
+        <v>-1.2734</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.214</v>
+        <v>-0.2676</v>
       </c>
       <c r="P3" t="n">
-        <v>1.6237</v>
+        <v>2.0876</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6237</v>
+        <v>2.0876</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1672</v>
+        <v>-0.402</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7512</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>0.416</v>
+        <v>-0.3354</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.0722</v>
+        <v>1.6083</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.8223</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0722</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7214</v>
+        <v>1.8222</v>
       </c>
       <c r="E4" t="n">
         <v>1.5185</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2029</v>
+        <v>0.3037</v>
       </c>
       <c r="G4" t="n">
         <v>0.8139</v>
@@ -766,13 +766,13 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1647</v>
+        <v>-0.0639</v>
       </c>
       <c r="T4" t="n">
         <v>-0.0747</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0901</v>
+        <v>0.0108</v>
       </c>
       <c r="V4" t="n">
         <v>1.0722</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. LOYD</t>
+          <t>K. JONES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6826</v>
+        <v>1.0295</v>
       </c>
       <c r="E5" t="n">
-        <v>2.9206</v>
+        <v>1.6071</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.238</v>
+        <v>-0.5776</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.1088</v>
+        <v>0.1881</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.1824</v>
+        <v>0.1814</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0736</v>
+        <v>0.0068</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4322</v>
+        <v>1.2963</v>
       </c>
       <c r="K5" t="n">
-        <v>0.091</v>
+        <v>1.0755</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3412</v>
+        <v>0.2208</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.5409</v>
+        <v>-1.1082</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.2734</v>
+        <v>-0.8942</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2676</v>
+        <v>-0.214</v>
       </c>
       <c r="P5" t="n">
-        <v>2.0876</v>
+        <v>1.6237</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0876</v>
+        <v>1.6237</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9045</v>
+        <v>0.2899</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3339</v>
+        <v>0.3108</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5706</v>
+        <v>-0.0209</v>
       </c>
       <c r="V5" t="n">
-        <v>1.6083</v>
+        <v>-1.0722</v>
       </c>
       <c r="W5" t="n">
-        <v>2.8223</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.214</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.197</v>
+        <v>0.2658</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1191</v>
+        <v>0.7835</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3161</v>
+        <v>-0.5177</v>
       </c>
       <c r="G6" t="n">
         <v>0.002</v>
@@ -922,13 +922,13 @@
         <v>1.8556</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.217</v>
+        <v>0.2458</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6326000000000001</v>
+        <v>0.0318</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4156</v>
+        <v>0.2139</v>
       </c>
       <c r="V6" t="n">
         <v>-0.6778999999999999</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3578</v>
+        <v>-0.1548</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.6233</v>
+        <v>-1.1515</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2655</v>
+        <v>0.9967</v>
       </c>
       <c r="G7" t="n">
         <v>-0.6855</v>
@@ -1000,13 +1000,13 @@
         <v>0.232</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0958</v>
+        <v>0.2987</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3734</v>
+        <v>0.0984</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4692</v>
+        <v>0.2003</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. HAZER</t>
+          <t>R. BEAUBOIS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6748</v>
+        <v>-0.3729</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6959</v>
+        <v>-0.055</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0212</v>
+        <v>-0.3178</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.7494</v>
+        <v>-0.7366</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0168</v>
+        <v>-2.4129</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7662</v>
+        <v>1.6763</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6959</v>
+        <v>0.1571</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0168</v>
+        <v>-1.5727</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7127</v>
+        <v>1.7298</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0535</v>
+        <v>-0.8938</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>-0.8401999999999999</v>
       </c>
       <c r="O8" t="n">
         <v>-0.0535</v>
       </c>
       <c r="P8" t="n">
-        <v>0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1573</v>
+        <v>-0.1002</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>-0.2122</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1573</v>
+        <v>0.112</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. BEAUBOIS</t>
+          <t>S. HAZER</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.676</v>
+        <v>-0.4389</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2909</v>
+        <v>-0.46</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3851</v>
+        <v>0.0212</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7366</v>
+        <v>-0.7494</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.4129</v>
+        <v>0.0168</v>
       </c>
       <c r="I9" t="n">
-        <v>1.6763</v>
+        <v>-0.7662</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1571</v>
+        <v>-0.6959</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.5727</v>
+        <v>0.0168</v>
       </c>
       <c r="L9" t="n">
-        <v>1.7298</v>
+        <v>-0.7127</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8938</v>
+        <v>-0.0535</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8401999999999999</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>-0.0535</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4033</v>
+        <v>0.0786</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4481</v>
+        <v>0.2359</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0448</v>
+        <v>-0.1573</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0149</v>
+        <v>-2.5306</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5714</v>
+        <v>-0.1796</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.5863</v>
+        <v>-2.351</v>
       </c>
       <c r="G10" t="n">
         <v>1.5982</v>
@@ -1234,13 +1234,13 @@
         <v>1.1598</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0312</v>
+        <v>-0.4845</v>
       </c>
       <c r="T10" t="n">
-        <v>0.9752</v>
+        <v>0.2243</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9441000000000001</v>
+        <v>-0.7088</v>
       </c>
       <c r="V10" t="n">
         <v>-1.3247</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C. SWIDER</t>
+          <t>I. CORDINIER</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.6494</v>
+        <v>-3.1152</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9524</v>
+        <v>-1.102</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6971</v>
+        <v>-2.0132</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.6574</v>
+        <v>-1.7282</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.6301</v>
+        <v>-2.7154</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.0273</v>
+        <v>0.9872</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.1309</v>
+        <v>-0.2375</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.7359</v>
+        <v>-1.5993</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.3949</v>
+        <v>1.3618</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.5265</v>
+        <v>-1.4907</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8942</v>
+        <v>-1.1161</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6323</v>
+        <v>-0.3746</v>
       </c>
       <c r="P11" t="n">
         <v>0.4639</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4639</v>
+        <v>1.6237</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9199000000000001</v>
+        <v>-0.3844</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8215</v>
+        <v>0.1535</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0984</v>
+        <v>-0.5379</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.5361</v>
+        <v>-1.4665</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.5361</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>I. CORDINIER</t>
+          <t>C. SWIDER</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.318</v>
+        <v>-3.4568</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.0023</v>
+        <v>-1.7597</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.3157</v>
+        <v>-1.6971</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.7282</v>
+        <v>-2.6574</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.7154</v>
+        <v>-1.6301</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9872</v>
+        <v>-1.0273</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.2375</v>
+        <v>-1.1309</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.5993</v>
+        <v>-0.7359</v>
       </c>
       <c r="L12" t="n">
-        <v>1.3618</v>
+        <v>-0.3949</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.4907</v>
+        <v>-1.5265</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.1161</v>
+        <v>-0.8942</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.3746</v>
+        <v>-0.6323</v>
       </c>
       <c r="P12" t="n">
         <v>0.4639</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.6237</v>
+        <v>0.4639</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.5872</v>
+        <v>-0.7272999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7468</v>
+        <v>-0.6289</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8404</v>
+        <v>-0.0984</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.4665</v>
+        <v>-0.5361</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.6083</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.6004</v>
+        <v>-5.5097</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.8611</v>
+        <v>-2.5688</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.7393</v>
+        <v>-2.941</v>
       </c>
       <c r="G13" t="n">
         <v>-2.8551</v>
@@ -1468,13 +1468,13 @@
         <v>1.1598</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7934</v>
+        <v>-0.116</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7512</v>
+        <v>0.0435</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0422</v>
+        <v>-0.1595</v>
       </c>
       <c r="V13" t="n">
         <v>-2.5387</v>
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-7.901999999999999</v>
+        <v>-7.155199999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5545</v>
+        <v>3.301199999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-10.4565</v>
+        <v>-10.4563</v>
       </c>
       <c r="G14" t="n">
-        <v>-4.614300000000001</v>
+        <v>-4.6143</v>
       </c>
       <c r="H14" t="n">
         <v>-12.2265</v>
@@ -1519,7 +1519,7 @@
         <v>7.612099999999998</v>
       </c>
       <c r="J14" t="n">
-        <v>8.577499999999999</v>
+        <v>8.577499999999997</v>
       </c>
       <c r="K14" t="n">
         <v>-1.4427</v>
@@ -1546,19 +1546,19 @@
         <v>12.7576</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.2799</v>
+        <v>-1.5333</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.725</v>
+        <v>0.02179999999999994</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.5551</v>
+        <v>-1.5552</v>
       </c>
       <c r="V14" t="n">
         <v>-3.327299999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>5.1396</v>
+        <v>5.139600000000001</v>
       </c>
       <c r="X14" t="n">
         <v>-8.466900000000001</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. HOLMES</t>
+          <t>C. OSMAN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.465</v>
+        <v>6.1877</v>
       </c>
       <c r="E15" t="n">
-        <v>4.0674</v>
+        <v>6.3956</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3976</v>
+        <v>-0.2079</v>
       </c>
       <c r="G15" t="n">
-        <v>1.7997</v>
+        <v>3.6976</v>
       </c>
       <c r="H15" t="n">
-        <v>3.0912</v>
+        <v>1.0746</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.2914</v>
+        <v>2.6231</v>
       </c>
       <c r="J15" t="n">
-        <v>2.3855</v>
+        <v>5.4418</v>
       </c>
       <c r="K15" t="n">
-        <v>2.2015</v>
+        <v>1.079</v>
       </c>
       <c r="L15" t="n">
-        <v>0.184</v>
+        <v>4.3628</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.5858</v>
+        <v>-1.7442</v>
       </c>
       <c r="N15" t="n">
-        <v>0.8897</v>
+        <v>-0.0044</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.4755</v>
+        <v>-1.7398</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.4639</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1598</v>
+        <v>-1.6237</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6959</v>
+        <v>1.6237</v>
       </c>
       <c r="S15" t="n">
-        <v>2.5519</v>
+        <v>0.74</v>
       </c>
       <c r="T15" t="n">
-        <v>1.7695</v>
+        <v>0.2912</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7824</v>
+        <v>0.4488</v>
       </c>
       <c r="V15" t="n">
-        <v>1.5773</v>
+        <v>1.7501</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0722</v>
+        <v>2.2862</v>
       </c>
       <c r="X15" t="n">
-        <v>0.5051</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. OSMAN</t>
+          <t>K. SLOUKAS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.2435</v>
+        <v>4.4172</v>
       </c>
       <c r="E16" t="n">
-        <v>5.2161</v>
+        <v>3.15</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0274</v>
+        <v>1.2672</v>
       </c>
       <c r="G16" t="n">
-        <v>3.6976</v>
+        <v>2.0803</v>
       </c>
       <c r="H16" t="n">
-        <v>1.0746</v>
+        <v>1.9231</v>
       </c>
       <c r="I16" t="n">
-        <v>2.6231</v>
+        <v>0.1573</v>
       </c>
       <c r="J16" t="n">
-        <v>5.4418</v>
+        <v>2.6054</v>
       </c>
       <c r="K16" t="n">
-        <v>1.079</v>
+        <v>1.2337</v>
       </c>
       <c r="L16" t="n">
-        <v>4.3628</v>
+        <v>1.3717</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.7442</v>
+        <v>-0.5251</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0044</v>
+        <v>0.6893</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.7398</v>
+        <v>-1.2144</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.3917</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.6237</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6237</v>
+        <v>1.3917</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2043</v>
+        <v>0.2673</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8883</v>
+        <v>-0.1333</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.4007</v>
       </c>
       <c r="V16" t="n">
-        <v>1.7501</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W16" t="n">
-        <v>2.2862</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. GRANT</t>
+          <t>R. HOLMES</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.5296</v>
+        <v>4.2861</v>
       </c>
       <c r="E17" t="n">
-        <v>5.8755</v>
+        <v>3.1238</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.3459</v>
+        <v>1.1623</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8957000000000001</v>
+        <v>1.7997</v>
       </c>
       <c r="H17" t="n">
-        <v>2.204</v>
+        <v>3.0912</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.3083</v>
+        <v>-1.2914</v>
       </c>
       <c r="J17" t="n">
-        <v>2.8686</v>
+        <v>2.3855</v>
       </c>
       <c r="K17" t="n">
-        <v>2.4906</v>
+        <v>2.2015</v>
       </c>
       <c r="L17" t="n">
-        <v>0.378</v>
+        <v>0.184</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.9729</v>
+        <v>-0.5858</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2866</v>
+        <v>0.8897</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.6862</v>
+        <v>-1.4755</v>
       </c>
       <c r="P17" t="n">
+        <v>-0.4639</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-1.1598</v>
+      </c>
+      <c r="R17" t="n">
         <v>0.6959</v>
       </c>
-      <c r="Q17" t="n">
-        <v>-0.4639</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.1598</v>
-      </c>
       <c r="S17" t="n">
-        <v>2.0076</v>
+        <v>1.373</v>
       </c>
       <c r="T17" t="n">
-        <v>2.3986</v>
+        <v>0.8259</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.391</v>
+        <v>0.5472</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9304</v>
+        <v>1.5773</v>
       </c>
       <c r="W17" t="n">
         <v>1.0722</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1418</v>
+        <v>0.5051</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>O. YURTSEVEN</t>
+          <t>J. GRANT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.1237</v>
+        <v>3.2651</v>
       </c>
       <c r="E18" t="n">
-        <v>5.5501</v>
+        <v>4.3421</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.4264</v>
+        <v>-1.077</v>
       </c>
       <c r="G18" t="n">
-        <v>2.7011</v>
+        <v>0.8957000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>2.7513</v>
+        <v>2.204</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0501</v>
+        <v>-1.3083</v>
       </c>
       <c r="J18" t="n">
-        <v>3.2732</v>
+        <v>2.8686</v>
       </c>
       <c r="K18" t="n">
-        <v>3.1628</v>
+        <v>2.4906</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1104</v>
+        <v>0.378</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5721000000000001</v>
+        <v>-1.9729</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4116</v>
+        <v>-0.2866</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1605</v>
+        <v>-1.6862</v>
       </c>
       <c r="P18" t="n">
         <v>0.6959</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.232</v>
+        <v>-0.4639</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8685</v>
+        <v>0.7431</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9006</v>
+        <v>0.8652</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0321</v>
+        <v>-0.1221</v>
       </c>
       <c r="V18" t="n">
+        <v>0.9304</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.0722</v>
+      </c>
+      <c r="X18" t="n">
         <v>-0.1418</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.6083</v>
-      </c>
-      <c r="X18" t="n">
-        <v>-1.7501</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K. SLOUKAS</t>
+          <t>O. YURTSEVEN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>4.0304</v>
+        <v>3.1972</v>
       </c>
       <c r="E19" t="n">
-        <v>3.032</v>
+        <v>4.7245</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9984</v>
+        <v>-1.5273</v>
       </c>
       <c r="G19" t="n">
-        <v>2.0803</v>
+        <v>2.7011</v>
       </c>
       <c r="H19" t="n">
-        <v>1.9231</v>
+        <v>2.7513</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1573</v>
+        <v>-0.0501</v>
       </c>
       <c r="J19" t="n">
-        <v>2.6054</v>
+        <v>3.2732</v>
       </c>
       <c r="K19" t="n">
-        <v>1.2337</v>
+        <v>3.1628</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3717</v>
+        <v>0.1104</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5251</v>
+        <v>-0.5721000000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6893</v>
+        <v>-0.4116</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.2144</v>
+        <v>-0.1605</v>
       </c>
       <c r="P19" t="n">
-        <v>1.3917</v>
+        <v>0.6959</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1195</v>
+        <v>-0.058</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2513</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1318</v>
+        <v>-0.1329</v>
       </c>
       <c r="V19" t="n">
-        <v>0.6778999999999999</v>
+        <v>-0.1418</v>
       </c>
       <c r="W19" t="n">
-        <v>0.6778999999999999</v>
+        <v>1.6083</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.7501</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.0368</v>
+        <v>2.4242</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8525</v>
+        <v>1.2064</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1842</v>
+        <v>1.2179</v>
       </c>
       <c r="G20" t="n">
         <v>1.8029</v>
@@ -2014,13 +2014,13 @@
         <v>0.6959</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2842</v>
+        <v>0.1032</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4402</v>
+        <v>-0.0863</v>
       </c>
       <c r="U20" t="n">
-        <v>0.156</v>
+        <v>0.1896</v>
       </c>
       <c r="V20" t="n">
         <v>1.214</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5865</v>
+        <v>0.5193</v>
       </c>
       <c r="E21" t="n">
         <v>-0.1736</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7602</v>
+        <v>0.6929</v>
       </c>
       <c r="G21" t="n">
         <v>0.2579</v>
@@ -2092,13 +2092,13 @@
         <v>0.4639</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1353</v>
+        <v>-0.2025</v>
       </c>
       <c r="T21" t="n">
         <v>-0.224</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0887</v>
+        <v>0.0215</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0834</v>
+        <v>0.0517</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3361</v>
+        <v>0.572</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4195</v>
+        <v>-0.5203</v>
       </c>
       <c r="G22" t="n">
         <v>-0.0751</v>
@@ -2170,13 +2170,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0083</v>
+        <v>0.1267</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>0.2359</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0083</v>
+        <v>-0.1092</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.7794</v>
+        <v>-0.7122000000000001</v>
       </c>
       <c r="E23" t="n">
         <v>-1.6027</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8232</v>
+        <v>0.8905</v>
       </c>
       <c r="G23" t="n">
         <v>-1.0641</v>
@@ -2248,13 +2248,13 @@
         <v>0.232</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0527</v>
+        <v>0.1199</v>
       </c>
       <c r="T23" t="n">
         <v>-0.0668</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1195</v>
+        <v>0.1867</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.8248</v>
+        <v>-1.6898</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.2207</v>
+        <v>0.0152</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.6042</v>
+        <v>-1.705</v>
       </c>
       <c r="G24" t="n">
         <v>-1.6617</v>
@@ -2326,13 +2326,13 @@
         <v>0.9278</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5548</v>
+        <v>-0.4197</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1494</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4055</v>
+        <v>-0.5063</v>
       </c>
       <c r="V24" t="n">
         <v>-0.5361</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.7973</v>
+        <v>-6.1739</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.9214</v>
+        <v>-5.3316</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.8759</v>
+        <v>-0.8423</v>
       </c>
       <c r="G25" t="n">
         <v>-3.6362</v>
@@ -2404,13 +2404,13 @@
         <v>1.6237</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.9291</v>
+        <v>-0.3058</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.0455</v>
+        <v>-0.4558</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1164</v>
+        <v>0.15</v>
       </c>
       <c r="V25" t="n">
         <v>-1.0722</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-8.628500000000001</v>
+        <v>-7.8707</v>
       </c>
       <c r="E26" t="n">
-        <v>-6.555</v>
+        <v>-5.9653</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.0734</v>
+        <v>-1.9054</v>
       </c>
       <c r="G26" t="n">
         <v>-2.1841</v>
@@ -2482,13 +2482,13 @@
         <v>0.6959</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.9651</v>
+        <v>-0.2074</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.4481</v>
+        <v>0.1417</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.5171</v>
+        <v>-0.349</v>
       </c>
       <c r="V26" t="n">
         <v>-1.0722</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>7.902100000000003</v>
+        <v>7.9019</v>
       </c>
       <c r="E27" t="n">
-        <v>10.4563</v>
+        <v>10.4564</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.5543</v>
+        <v>-2.5544</v>
       </c>
       <c r="G27" t="n">
         <v>4.614</v>
@@ -2539,7 +2539,7 @@
         <v>10.7837</v>
       </c>
       <c r="L27" t="n">
-        <v>2.408000000000001</v>
+        <v>2.407999999999999</v>
       </c>
       <c r="M27" t="n">
         <v>-8.5777</v>
@@ -2560,19 +2560,19 @@
         <v>10.4381</v>
       </c>
       <c r="S27" t="n">
-        <v>2.2801</v>
+        <v>2.279799999999999</v>
       </c>
       <c r="T27" t="n">
         <v>1.5551</v>
       </c>
       <c r="U27" t="n">
-        <v>0.7248000000000002</v>
+        <v>0.7250000000000001</v>
       </c>
       <c r="V27" t="n">
         <v>3.327399999999999</v>
       </c>
       <c r="W27" t="n">
-        <v>8.466899999999999</v>
+        <v>8.466900000000001</v>
       </c>
       <c r="X27" t="n">
         <v>-5.1395</v>
